--- a/artfynd/A 52046-2022 artfynd.xlsx
+++ b/artfynd/A 52046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124729911</v>
+        <v>80139019</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nabben, Nabben, Srm</t>
+          <t>Tveta friluftsgård, 300 m V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648345</v>
+        <v>648223</v>
       </c>
       <c r="R2" t="n">
-        <v>6560630</v>
+        <v>6560420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,139 +762,32 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124729911</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>102077473</v>
-      </c>
-      <c r="B3" t="n">
-        <v>99153</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>219874</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tvetaspåret, Tveta, Srm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>647721</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6560695</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Södertälje</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tveta</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2022-07-05</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Åsa Johansson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Åsa Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/102077473</t>
+          <t>https://artportalen.se/Sighting/80139019</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52046-2022 artfynd.xlsx
+++ b/artfynd/A 52046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80139019</v>
+        <v>124729911</v>
       </c>
       <c r="B2" t="n">
-        <v>91409</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5741</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tveta friluftsgård, 300 m V om, Srm</t>
+          <t>Nabben, Nabben, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648223</v>
+        <v>648345</v>
       </c>
       <c r="R2" t="n">
-        <v>6560420</v>
+        <v>6560630</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-27</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,32 +762,139 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80139019</t>
+          <t>https://artportalen.se/Sighting/124729911</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102077473</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tvetaspåret, Tveta, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>647721</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6560695</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tveta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åsa Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102077473</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52046-2022 artfynd.xlsx
+++ b/artfynd/A 52046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124729911</v>
+        <v>80139019</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5741</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nabben, Nabben, Srm</t>
+          <t>Tveta friluftsgård, 300 m V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648345</v>
+        <v>648223</v>
       </c>
       <c r="R2" t="n">
-        <v>6560630</v>
+        <v>6560420</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2019-09-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,73 +762,70 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124729911</t>
+          <t>https://artportalen.se/Sighting/80139019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102077473</v>
+        <v>124729911</v>
       </c>
       <c r="B3" t="n">
-        <v>99153</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tvetaspåret, Tveta, Srm</t>
+          <t>Nabben, Nabben, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647721</v>
+        <v>648345</v>
       </c>
       <c r="R3" t="n">
-        <v>6560695</v>
+        <v>6560630</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,23 +866,133 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Åsa Johansson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åsa Johansson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124729911</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102077473</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tvetaspåret, Tveta, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>647721</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6560695</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tveta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åsa Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/102077473</t>
         </is>
@@ -895,6 +1002,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
